--- a/DEVELOPMENT_ALL_OLD_NEW/M&S/M&S.0040 - mid indigo.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/M&S/M&S.0040 - mid indigo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\M&amp;S\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5BF966-B6CE-4D65-B8EB-F4D0783AEDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEF1FD0-8B8B-4149-98E3-7EF8400A6D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="mühendisler">[1]Sayfa6!$A$2:$A$10</definedName>
     <definedName name="Müşteriler">[1]Sayfa6!$B$2:$B$20</definedName>
     <definedName name="NEW">[2]DATA!$C$2:$C$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">SABLON!$A$1:$K$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">SABLON!$A$1:$K$73</definedName>
     <definedName name="SUPERVISOR">[2]DATA!$B$2:$B$13</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t>dcr</t>
   </si>
@@ -208,9 +208,6 @@
   </si>
   <si>
     <t>Disperse</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>LUBRCANT</t>
@@ -1438,7 +1435,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1690,27 +1687,6 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="49" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="50" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1861,6 +1837,234 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="5" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="41" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1868,9 +2072,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1885,287 +2086,59 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="5" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2462,15 +2435,14 @@
     <sheetNames>
       <sheetName val="ALL SAMPLES"/>
       <sheetName val="Sheet1"/>
+      <sheetName val="DATA"/>
       <sheetName val="CUSTOMER"/>
-      <sheetName val="DATA"/>
       <sheetName val="SABLON"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="2">
         <row r="2">
           <cell r="B2" t="str">
             <v>BILAL</v>
@@ -2518,6 +2490,7 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
@@ -2790,7 +2763,7 @@
   <sheetPr codeName="Sayfa3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="5" customWidth="1"/>
@@ -3585,21 +3558,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="156">
+      <c r="C2" s="183">
         <v>46217</v>
       </c>
-      <c r="D2" s="157"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="156" t="s">
+      <c r="D2" s="184"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="157"/>
-      <c r="H2" s="159" t="s">
+      <c r="G2" s="184"/>
+      <c r="H2" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="161"/>
+      <c r="I2" s="187"/>
+      <c r="J2" s="187"/>
+      <c r="K2" s="188"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -3608,17 +3581,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="156" t="s">
+      <c r="C3" s="183" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="157"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="168" t="s">
+      <c r="D3" s="184"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="189"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="169"/>
+      <c r="I3" s="196"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -3629,17 +3602,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="170" t="s">
+      <c r="C4" s="197" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="171"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="174"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="199"/>
+      <c r="F4" s="191"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="200"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="201"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -3648,17 +3621,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="175">
+      <c r="C5" s="202">
         <v>5122021135</v>
       </c>
-      <c r="D5" s="176"/>
-      <c r="E5" s="177"/>
-      <c r="F5" s="164"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="155"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="204"/>
+      <c r="F5" s="191"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="172"/>
+      <c r="K5" s="173"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -3667,17 +3640,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="178" t="s">
+      <c r="C6" s="205" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="179"/>
-      <c r="E6" s="180"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="155"/>
-      <c r="J6" s="154"/>
-      <c r="K6" s="155"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="192"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="173"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -3686,17 +3659,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="151" t="s">
+      <c r="C7" s="211" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="152"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="154"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="154"/>
-      <c r="K7" s="155"/>
+      <c r="D7" s="212"/>
+      <c r="E7" s="213"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="172"/>
+      <c r="K7" s="173"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -3705,15 +3678,15 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="181"/>
-      <c r="D8" s="182"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="165"/>
+      <c r="C8" s="214"/>
+      <c r="D8" s="215"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="192"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="154"/>
-      <c r="K8" s="155"/>
+      <c r="J8" s="172"/>
+      <c r="K8" s="173"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -3722,17 +3695,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="184">
+      <c r="C9" s="180">
         <v>7</v>
       </c>
-      <c r="D9" s="185"/>
-      <c r="E9" s="186"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="165"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="182"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="192"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="154"/>
-      <c r="K9" s="155"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="173"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -3741,15 +3714,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="184"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="186"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="165"/>
+      <c r="C10" s="180"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="182"/>
+      <c r="F10" s="191"/>
+      <c r="G10" s="192"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="154"/>
-      <c r="K10" s="155"/>
+      <c r="J10" s="172"/>
+      <c r="K10" s="173"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -3758,15 +3731,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="187"/>
-      <c r="D11" s="188"/>
-      <c r="E11" s="189"/>
-      <c r="F11" s="164"/>
-      <c r="G11" s="165"/>
-      <c r="H11" s="154"/>
-      <c r="I11" s="155"/>
-      <c r="J11" s="154"/>
-      <c r="K11" s="155"/>
+      <c r="C11" s="177"/>
+      <c r="D11" s="178"/>
+      <c r="E11" s="179"/>
+      <c r="F11" s="191"/>
+      <c r="G11" s="192"/>
+      <c r="H11" s="172"/>
+      <c r="I11" s="173"/>
+      <c r="J11" s="172"/>
+      <c r="K11" s="173"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -3775,17 +3748,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="190" t="s">
+      <c r="C12" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="191"/>
-      <c r="E12" s="192"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="165"/>
-      <c r="H12" s="154"/>
-      <c r="I12" s="155"/>
-      <c r="J12" s="154"/>
-      <c r="K12" s="155"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="191"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="172"/>
+      <c r="I12" s="173"/>
+      <c r="J12" s="172"/>
+      <c r="K12" s="173"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -3794,15 +3767,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="187"/>
-      <c r="D13" s="188"/>
-      <c r="E13" s="189"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="167"/>
-      <c r="H13" s="154"/>
-      <c r="I13" s="155"/>
-      <c r="J13" s="154"/>
-      <c r="K13" s="155"/>
+      <c r="C13" s="177"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="179"/>
+      <c r="F13" s="193"/>
+      <c r="G13" s="194"/>
+      <c r="H13" s="172"/>
+      <c r="I13" s="173"/>
+      <c r="J13" s="172"/>
+      <c r="K13" s="173"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -3811,17 +3784,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="193"/>
-      <c r="D14" s="193"/>
-      <c r="E14" s="194"/>
-      <c r="F14" s="195" t="s">
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="218"/>
+      <c r="F14" s="219" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="196"/>
-      <c r="H14" s="199" t="s">
+      <c r="G14" s="220"/>
+      <c r="H14" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="200"/>
+      <c r="I14" s="224"/>
       <c r="J14" s="16"/>
       <c r="K14" s="17"/>
       <c r="L14" s="4"/>
@@ -3839,14 +3812,14 @@
       <c r="E15" s="21">
         <v>1</v>
       </c>
-      <c r="F15" s="197"/>
-      <c r="G15" s="198"/>
-      <c r="H15" s="197"/>
-      <c r="I15" s="201"/>
-      <c r="J15" s="202" t="s">
+      <c r="F15" s="221"/>
+      <c r="G15" s="222"/>
+      <c r="H15" s="221"/>
+      <c r="I15" s="225"/>
+      <c r="J15" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="204" t="s">
+      <c r="K15" s="163" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -3872,27 +3845,27 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="206" t="s">
+      <c r="H16" s="165" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="206"/>
-      <c r="J16" s="203"/>
-      <c r="K16" s="205"/>
+      <c r="I16" s="165"/>
+      <c r="J16" s="162"/>
+      <c r="K16" s="164"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
     <row r="17" spans="1:13" ht="98.1" customHeight="1">
       <c r="A17" s="26"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="207" t="s">
+      <c r="C17" s="166" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="208"/>
-      <c r="E17" s="208"/>
-      <c r="F17" s="208"/>
-      <c r="G17" s="208"/>
-      <c r="H17" s="208"/>
-      <c r="I17" s="209"/>
+      <c r="D17" s="167"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="167"/>
+      <c r="H17" s="167"/>
+      <c r="I17" s="168"/>
       <c r="J17" s="28"/>
       <c r="K17" s="29"/>
       <c r="L17" s="25"/>
@@ -3916,13 +3889,13 @@
     <row r="19" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A19" s="26"/>
       <c r="B19" s="33"/>
-      <c r="C19" s="210"/>
-      <c r="D19" s="211"/>
-      <c r="E19" s="211"/>
-      <c r="F19" s="211"/>
-      <c r="G19" s="211"/>
-      <c r="H19" s="211"/>
-      <c r="I19" s="212"/>
+      <c r="C19" s="169"/>
+      <c r="D19" s="170"/>
+      <c r="E19" s="170"/>
+      <c r="F19" s="170"/>
+      <c r="G19" s="170"/>
+      <c r="H19" s="170"/>
+      <c r="I19" s="171"/>
       <c r="J19" s="34"/>
       <c r="K19" s="35"/>
       <c r="L19" s="25"/>
@@ -3948,10 +3921,10 @@
       <c r="G20" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="213" t="s">
+      <c r="H20" s="226" t="s">
         <v>55</v>
       </c>
-      <c r="I20" s="214"/>
+      <c r="I20" s="227"/>
       <c r="J20" s="82"/>
       <c r="K20" s="83"/>
       <c r="L20" s="25"/>
@@ -3965,10 +3938,10 @@
       <c r="E21" s="86"/>
       <c r="F21" s="86"/>
       <c r="G21" s="87"/>
-      <c r="H21" s="213" t="s">
-        <v>57</v>
-      </c>
-      <c r="I21" s="214"/>
+      <c r="H21" s="226" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="227"/>
       <c r="J21" s="82"/>
       <c r="K21" s="83"/>
       <c r="L21" s="25"/>
@@ -3976,284 +3949,292 @@
     </row>
     <row r="22" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A22" s="26"/>
-      <c r="B22" s="88"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="215" t="s">
-        <v>56</v>
-      </c>
-      <c r="I22" s="215"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="83"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="42"/>
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
     </row>
     <row r="23" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A23" s="26"/>
-      <c r="B23" s="90"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="96"/>
+      <c r="B23" s="90" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="91">
+        <v>35</v>
+      </c>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83">
+        <v>3</v>
+      </c>
+      <c r="G23" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="160" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="160"/>
+      <c r="J23" s="82"/>
+      <c r="K23" s="94"/>
       <c r="L23" s="25"/>
       <c r="M23" s="25"/>
     </row>
     <row r="24" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A24" s="26"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="42"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="83">
+        <v>100</v>
+      </c>
+      <c r="G24" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="147" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" s="147"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="96"/>
       <c r="L24" s="25"/>
       <c r="M24" s="25"/>
     </row>
-    <row r="25" spans="1:13" ht="74.099999999999994" customHeight="1">
+    <row r="25" spans="1:13" ht="73.8" customHeight="1">
       <c r="A25" s="26"/>
-      <c r="B25" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="98">
-        <v>35</v>
-      </c>
-      <c r="D25" s="83">
-        <v>40</v>
-      </c>
-      <c r="E25" s="83">
-        <v>60</v>
-      </c>
-      <c r="F25" s="83">
-        <v>3</v>
-      </c>
-      <c r="G25" s="99" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" s="220" t="s">
-        <v>38</v>
-      </c>
-      <c r="I25" s="220"/>
-      <c r="J25" s="82"/>
-      <c r="K25" s="101"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="96"/>
       <c r="L25" s="25"/>
       <c r="M25" s="25"/>
     </row>
     <row r="26" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A26" s="26"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="83">
-        <v>100</v>
-      </c>
-      <c r="G26" s="99" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="216" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" s="216"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="103"/>
+      <c r="B26" s="97"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="102"/>
       <c r="L26" s="25"/>
       <c r="M26" s="25"/>
     </row>
     <row r="27" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A27" s="26"/>
-      <c r="B27" s="100"/>
+      <c r="B27" s="84" t="s">
+        <v>40</v>
+      </c>
       <c r="C27" s="86"/>
       <c r="D27" s="86"/>
       <c r="E27" s="86"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="216"/>
-      <c r="I27" s="216"/>
-      <c r="J27" s="102"/>
-      <c r="K27" s="103"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="157"/>
+      <c r="I27" s="157"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
       <c r="L27" s="25"/>
       <c r="M27" s="25"/>
     </row>
     <row r="28" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A28" s="26"/>
-      <c r="B28" s="104"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="109"/>
+      <c r="B28" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="157"/>
+      <c r="I28" s="157"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
       <c r="L28" s="25"/>
       <c r="M28" s="25"/>
     </row>
     <row r="29" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A29" s="26"/>
-      <c r="B29" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="86"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="102"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="217"/>
-      <c r="I29" s="217"/>
-      <c r="J29" s="102"/>
-      <c r="K29" s="102"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="105"/>
       <c r="L29" s="25"/>
       <c r="M29" s="25"/>
     </row>
     <row r="30" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A30" s="26"/>
-      <c r="B30" s="100" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="86"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="217"/>
-      <c r="I30" s="217"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
+      <c r="B30" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="106">
+        <v>5</v>
+      </c>
+      <c r="D30" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="106">
+        <v>60</v>
+      </c>
+      <c r="F30" s="107">
+        <v>3</v>
+      </c>
+      <c r="G30" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="158" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="159"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="107"/>
       <c r="L30" s="25"/>
       <c r="M30" s="25"/>
     </row>
     <row r="31" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A31" s="26"/>
-      <c r="B31" s="110"/>
-      <c r="C31" s="111"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="110"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="112"/>
+      <c r="B31" s="109" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="107"/>
+      <c r="G31" s="108" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="158" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" s="159"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="107"/>
       <c r="L31" s="25"/>
       <c r="M31" s="25"/>
     </row>
     <row r="32" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A32" s="26"/>
-      <c r="B32" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="113">
-        <v>5</v>
-      </c>
-      <c r="D32" s="113" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="113">
-        <v>60</v>
-      </c>
-      <c r="F32" s="114">
-        <v>3</v>
-      </c>
-      <c r="G32" s="115" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="218" t="s">
-        <v>43</v>
-      </c>
-      <c r="I32" s="219"/>
-      <c r="J32" s="114"/>
-      <c r="K32" s="114"/>
+      <c r="B32" s="103"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="103"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="105"/>
       <c r="L32" s="25"/>
       <c r="M32" s="25"/>
     </row>
     <row r="33" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A33" s="26"/>
-      <c r="B33" s="116" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="117"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="117"/>
-      <c r="F33" s="114"/>
-      <c r="G33" s="115" t="s">
+      <c r="B33" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="86">
+        <v>3</v>
+      </c>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86">
+        <v>60</v>
+      </c>
+      <c r="F33" s="111">
+        <v>50</v>
+      </c>
+      <c r="G33" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="H33" s="218" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="219"/>
-      <c r="J33" s="114"/>
-      <c r="K33" s="114"/>
+      <c r="H33" s="146" t="s">
+        <v>47</v>
+      </c>
+      <c r="I33" s="146"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="83"/>
       <c r="L33" s="25"/>
       <c r="M33" s="25"/>
     </row>
     <row r="34" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A34" s="26"/>
-      <c r="B34" s="110"/>
-      <c r="C34" s="111"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111"/>
-      <c r="F34" s="112"/>
-      <c r="G34" s="112"/>
-      <c r="H34" s="110"/>
-      <c r="I34" s="110"/>
-      <c r="J34" s="112"/>
-      <c r="K34" s="112"/>
+      <c r="B34" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="147"/>
+      <c r="I34" s="147"/>
+      <c r="J34" s="83"/>
+      <c r="K34" s="83"/>
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
     </row>
     <row r="35" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A35" s="26"/>
-      <c r="B35" s="100" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="86">
-        <v>3</v>
-      </c>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86">
-        <v>60</v>
-      </c>
-      <c r="F35" s="118">
-        <v>50</v>
-      </c>
-      <c r="G35" s="119" t="s">
-        <v>36</v>
-      </c>
-      <c r="H35" s="150" t="s">
-        <v>47</v>
-      </c>
-      <c r="I35" s="150"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
+      <c r="B35" s="113"/>
+      <c r="C35" s="114"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="115"/>
+      <c r="G35" s="116"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="117"/>
+      <c r="J35" s="115"/>
+      <c r="K35" s="115"/>
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
     </row>
     <row r="36" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A36" s="26"/>
-      <c r="B36" s="100" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="86"/>
-      <c r="D36" s="86"/>
-      <c r="E36" s="86"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="216"/>
-      <c r="I36" s="216"/>
+      <c r="B36" s="93" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="86">
+        <v>5</v>
+      </c>
+      <c r="D36" s="86">
+        <v>50</v>
+      </c>
+      <c r="E36" s="86">
+        <v>70</v>
+      </c>
+      <c r="F36" s="95">
+        <v>1</v>
+      </c>
+      <c r="G36" s="118" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" s="146" t="s">
+        <v>49</v>
+      </c>
+      <c r="I36" s="146"/>
       <c r="J36" s="83"/>
       <c r="K36" s="83"/>
       <c r="L36" s="25"/>
@@ -4261,43 +4242,35 @@
     </row>
     <row r="37" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A37" s="26"/>
-      <c r="B37" s="120"/>
-      <c r="C37" s="121"/>
-      <c r="D37" s="121"/>
-      <c r="E37" s="121"/>
-      <c r="F37" s="122"/>
-      <c r="G37" s="123"/>
-      <c r="H37" s="109"/>
-      <c r="I37" s="124"/>
-      <c r="J37" s="122"/>
-      <c r="K37" s="122"/>
+      <c r="B37" s="93"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="86"/>
+      <c r="E37" s="86"/>
+      <c r="F37" s="95">
+        <v>100</v>
+      </c>
+      <c r="G37" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="147" t="s">
+        <v>50</v>
+      </c>
+      <c r="I37" s="147"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
       <c r="L37" s="25"/>
       <c r="M37" s="25"/>
     </row>
     <row r="38" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A38" s="26"/>
-      <c r="B38" s="100" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="86">
-        <v>5</v>
-      </c>
-      <c r="D38" s="86">
-        <v>50</v>
-      </c>
-      <c r="E38" s="86">
-        <v>70</v>
-      </c>
-      <c r="F38" s="102">
-        <v>1</v>
-      </c>
-      <c r="G38" s="125" t="s">
-        <v>52</v>
-      </c>
-      <c r="H38" s="150" t="s">
-        <v>49</v>
-      </c>
-      <c r="I38" s="150"/>
+      <c r="B38" s="93"/>
+      <c r="C38" s="86"/>
+      <c r="D38" s="86"/>
+      <c r="E38" s="86"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
       <c r="J38" s="83"/>
       <c r="K38" s="83"/>
       <c r="L38" s="25"/>
@@ -4305,351 +4278,345 @@
     </row>
     <row r="39" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A39" s="26"/>
-      <c r="B39" s="100"/>
-      <c r="C39" s="86"/>
-      <c r="D39" s="86"/>
-      <c r="E39" s="86"/>
-      <c r="F39" s="102">
-        <v>100</v>
-      </c>
-      <c r="G39" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="H39" s="216" t="s">
-        <v>50</v>
-      </c>
-      <c r="I39" s="216"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
+      <c r="B39" s="119"/>
+      <c r="C39" s="120"/>
+      <c r="D39" s="208"/>
+      <c r="E39" s="208"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="121"/>
+      <c r="H39" s="149"/>
+      <c r="I39" s="149"/>
+      <c r="J39" s="121"/>
+      <c r="K39" s="121"/>
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
     </row>
     <row r="40" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A40" s="26"/>
-      <c r="B40" s="100"/>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
-      <c r="E40" s="86"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="216"/>
-      <c r="I40" s="216"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
+      <c r="B40" s="122" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="123">
+        <v>2</v>
+      </c>
+      <c r="D40" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="124">
+        <v>100</v>
+      </c>
+      <c r="F40" s="125">
+        <v>1</v>
+      </c>
+      <c r="G40" s="112" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" s="150" t="s">
+        <v>53</v>
+      </c>
+      <c r="I40" s="150"/>
+      <c r="J40" s="126"/>
+      <c r="K40" s="127"/>
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
     </row>
     <row r="41" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A41" s="26"/>
-      <c r="B41" s="126"/>
-      <c r="C41" s="127"/>
-      <c r="D41" s="147"/>
-      <c r="E41" s="147"/>
+      <c r="B41" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="126"/>
+      <c r="D41" s="126"/>
+      <c r="E41" s="126"/>
       <c r="F41" s="128"/>
-      <c r="G41" s="128"/>
-      <c r="H41" s="222"/>
-      <c r="I41" s="222"/>
-      <c r="J41" s="128"/>
-      <c r="K41" s="128"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="209"/>
+      <c r="I41" s="209"/>
+      <c r="J41" s="126"/>
+      <c r="K41" s="126"/>
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
     </row>
     <row r="42" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A42" s="26"/>
-      <c r="B42" s="129" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="130">
-        <v>2</v>
-      </c>
-      <c r="D42" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="131">
-        <v>100</v>
-      </c>
-      <c r="F42" s="132">
-        <v>1</v>
-      </c>
-      <c r="G42" s="119" t="s">
-        <v>52</v>
-      </c>
-      <c r="H42" s="223" t="s">
-        <v>53</v>
-      </c>
-      <c r="I42" s="223"/>
-      <c r="J42" s="133"/>
-      <c r="K42" s="134"/>
+      <c r="B42" s="129"/>
+      <c r="C42" s="130"/>
+      <c r="D42" s="130"/>
+      <c r="E42" s="130"/>
+      <c r="F42" s="130"/>
+      <c r="G42" s="130"/>
+      <c r="H42" s="102"/>
+      <c r="I42" s="131"/>
+      <c r="J42" s="115"/>
+      <c r="K42" s="115"/>
       <c r="L42" s="25"/>
       <c r="M42" s="25"/>
     </row>
     <row r="43" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A43" s="26"/>
-      <c r="B43" s="89" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="133"/>
-      <c r="D43" s="133"/>
-      <c r="E43" s="133"/>
-      <c r="F43" s="135"/>
-      <c r="G43" s="134"/>
-      <c r="H43" s="148"/>
-      <c r="I43" s="148"/>
-      <c r="J43" s="133"/>
-      <c r="K43" s="133"/>
+      <c r="B43" s="93"/>
+      <c r="C43" s="86"/>
+      <c r="D43" s="86"/>
+      <c r="E43" s="86"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="151"/>
+      <c r="I43" s="152"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="83"/>
       <c r="L43" s="25"/>
       <c r="M43" s="25"/>
     </row>
     <row r="44" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A44" s="26"/>
-      <c r="B44" s="136"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="137"/>
-      <c r="E44" s="137"/>
-      <c r="F44" s="137"/>
-      <c r="G44" s="137"/>
-      <c r="H44" s="109"/>
-      <c r="I44" s="138"/>
-      <c r="J44" s="122"/>
-      <c r="K44" s="122"/>
+      <c r="B44" s="93"/>
+      <c r="C44" s="86"/>
+      <c r="D44" s="86"/>
+      <c r="E44" s="86"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="151"/>
+      <c r="I44" s="152"/>
+      <c r="J44" s="83"/>
+      <c r="K44" s="83"/>
       <c r="L44" s="25"/>
       <c r="M44" s="25"/>
     </row>
     <row r="45" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A45" s="26"/>
-      <c r="B45" s="100"/>
-      <c r="C45" s="86"/>
-      <c r="D45" s="86"/>
-      <c r="E45" s="86"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="224"/>
-      <c r="I45" s="225"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="83"/>
+      <c r="B45" s="129"/>
+      <c r="C45" s="130"/>
+      <c r="D45" s="130"/>
+      <c r="E45" s="130"/>
+      <c r="F45" s="130"/>
+      <c r="G45" s="130"/>
+      <c r="H45" s="102"/>
+      <c r="I45" s="131"/>
+      <c r="J45" s="115"/>
+      <c r="K45" s="115"/>
       <c r="L45" s="25"/>
       <c r="M45" s="25"/>
     </row>
     <row r="46" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A46" s="26"/>
-      <c r="B46" s="100"/>
-      <c r="C46" s="86"/>
-      <c r="D46" s="86"/>
-      <c r="E46" s="86"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="224"/>
-      <c r="I46" s="225"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
+      <c r="B46" s="132"/>
+      <c r="C46" s="133"/>
+      <c r="D46" s="134"/>
+      <c r="E46" s="134"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="112"/>
+      <c r="H46" s="150"/>
+      <c r="I46" s="150"/>
+      <c r="J46" s="95"/>
+      <c r="K46" s="92"/>
       <c r="L46" s="25"/>
       <c r="M46" s="25"/>
     </row>
     <row r="47" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A47" s="26"/>
-      <c r="B47" s="136"/>
-      <c r="C47" s="137"/>
-      <c r="D47" s="137"/>
+      <c r="B47" s="132"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
       <c r="E47" s="137"/>
-      <c r="F47" s="137"/>
-      <c r="G47" s="137"/>
-      <c r="H47" s="109"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="122"/>
-      <c r="K47" s="122"/>
+      <c r="F47" s="138"/>
+      <c r="G47" s="92"/>
+      <c r="H47" s="153"/>
+      <c r="I47" s="153"/>
+      <c r="J47" s="95"/>
+      <c r="K47" s="95"/>
       <c r="L47" s="25"/>
       <c r="M47" s="25"/>
     </row>
     <row r="48" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A48" s="26"/>
-      <c r="B48" s="139"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="141"/>
-      <c r="E48" s="141"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="119"/>
-      <c r="H48" s="223"/>
-      <c r="I48" s="223"/>
-      <c r="J48" s="102"/>
-      <c r="K48" s="99"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="106"/>
+      <c r="D48" s="106"/>
+      <c r="E48" s="106"/>
+      <c r="F48" s="107"/>
+      <c r="G48" s="107"/>
+      <c r="H48" s="210"/>
+      <c r="I48" s="210"/>
+      <c r="J48" s="139"/>
+      <c r="K48" s="139"/>
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
     </row>
     <row r="49" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A49" s="26"/>
-      <c r="B49" s="139"/>
-      <c r="C49" s="143"/>
-      <c r="D49" s="143"/>
-      <c r="E49" s="144"/>
-      <c r="F49" s="145"/>
-      <c r="G49" s="99"/>
-      <c r="H49" s="226"/>
-      <c r="I49" s="226"/>
-      <c r="J49" s="102"/>
-      <c r="K49" s="102"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="143"/>
+      <c r="I49" s="144"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="69"/>
       <c r="L49" s="25"/>
       <c r="M49" s="25"/>
     </row>
     <row r="50" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A50" s="26"/>
-      <c r="B50" s="88"/>
-      <c r="C50" s="113"/>
-      <c r="D50" s="113"/>
-      <c r="E50" s="113"/>
-      <c r="F50" s="114"/>
-      <c r="G50" s="114"/>
-      <c r="H50" s="149"/>
-      <c r="I50" s="149"/>
-      <c r="J50" s="146"/>
-      <c r="K50" s="146"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="154"/>
+      <c r="I50" s="155"/>
+      <c r="J50" s="49"/>
+      <c r="K50" s="49"/>
       <c r="L50" s="25"/>
       <c r="M50" s="25"/>
     </row>
-    <row r="51" spans="1:13" ht="74.099999999999994" customHeight="1">
+    <row r="51" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A51" s="26"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="69"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="227"/>
-      <c r="I51" s="228"/>
-      <c r="J51" s="70"/>
-      <c r="K51" s="69"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
       <c r="L51" s="25"/>
       <c r="M51" s="25"/>
     </row>
-    <row r="52" spans="1:13" ht="74.099999999999994" customHeight="1">
+    <row r="52" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A52" s="26"/>
-      <c r="B52" s="46"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="229"/>
-      <c r="I52" s="230"/>
-      <c r="J52" s="49"/>
-      <c r="K52" s="49"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="60"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="156"/>
+      <c r="I52" s="156"/>
+      <c r="J52" s="45"/>
+      <c r="K52" s="51"/>
       <c r="L52" s="25"/>
       <c r="M52" s="25"/>
     </row>
     <row r="53" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A53" s="26"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="55"/>
-      <c r="J53" s="52"/>
-      <c r="K53" s="52"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="61"/>
+      <c r="D53" s="61"/>
+      <c r="E53" s="62"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="148"/>
+      <c r="I53" s="148"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
       <c r="L53" s="25"/>
       <c r="M53" s="25"/>
     </row>
     <row r="54" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A54" s="26"/>
-      <c r="B54" s="57"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="59"/>
-      <c r="F54" s="60"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="231"/>
-      <c r="I54" s="231"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="51"/>
+      <c r="B54" s="64"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="142"/>
+      <c r="I54" s="142"/>
+      <c r="J54" s="67"/>
+      <c r="K54" s="67"/>
       <c r="L54" s="25"/>
       <c r="M54" s="25"/>
     </row>
-    <row r="55" spans="1:13" ht="71.099999999999994" customHeight="1">
+    <row r="55" spans="1:13" ht="77.099999999999994" customHeight="1">
       <c r="A55" s="26"/>
-      <c r="B55" s="57"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="62"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="221"/>
-      <c r="I55" s="221"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="45"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="69"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="143"/>
+      <c r="I55" s="144"/>
+      <c r="J55" s="70"/>
+      <c r="K55" s="69"/>
       <c r="L55" s="25"/>
       <c r="M55" s="25"/>
     </row>
-    <row r="56" spans="1:13" ht="71.099999999999994" customHeight="1">
-      <c r="A56" s="26"/>
-      <c r="B56" s="64"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="65"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="66"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="234"/>
-      <c r="I56" s="234"/>
-      <c r="J56" s="67"/>
-      <c r="K56" s="67"/>
-      <c r="L56" s="25"/>
-      <c r="M56" s="25"/>
-    </row>
-    <row r="57" spans="1:13" ht="77.099999999999994" customHeight="1">
-      <c r="A57" s="26"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="69"/>
-      <c r="D57" s="69"/>
-      <c r="E57" s="69"/>
-      <c r="F57" s="69"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="227"/>
-      <c r="I57" s="228"/>
-      <c r="J57" s="70"/>
-      <c r="K57" s="69"/>
-      <c r="L57" s="25"/>
-      <c r="M57" s="25"/>
+    <row r="56" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A56" s="53"/>
+      <c r="B56" s="71"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="140"/>
+      <c r="I56" s="141"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="43"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="54"/>
+    </row>
+    <row r="57" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A57" s="53"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="145"/>
+      <c r="I57" s="145"/>
+      <c r="J57" s="73"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="54"/>
     </row>
     <row r="58" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A58" s="53"/>
-      <c r="B58" s="71"/>
+      <c r="B58" s="74"/>
       <c r="C58" s="43"/>
       <c r="D58" s="43"/>
       <c r="E58" s="43"/>
       <c r="F58" s="43"/>
       <c r="G58" s="43"/>
-      <c r="H58" s="232"/>
-      <c r="I58" s="233"/>
+      <c r="H58" s="140"/>
+      <c r="I58" s="141"/>
       <c r="J58" s="72"/>
-      <c r="K58" s="43"/>
+      <c r="K58" s="75"/>
       <c r="L58" s="4"/>
       <c r="M58" s="54"/>
     </row>
     <row r="59" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A59" s="53"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="235"/>
-      <c r="I59" s="235"/>
-      <c r="J59" s="73"/>
-      <c r="K59" s="49"/>
+      <c r="B59" s="76"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="140"/>
+      <c r="I59" s="141"/>
+      <c r="J59" s="72"/>
+      <c r="K59" s="75"/>
       <c r="L59" s="4"/>
       <c r="M59" s="54"/>
     </row>
     <row r="60" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A60" s="53"/>
-      <c r="B60" s="74"/>
+      <c r="B60" s="76"/>
       <c r="C60" s="43"/>
       <c r="D60" s="43"/>
       <c r="E60" s="43"/>
       <c r="F60" s="43"/>
       <c r="G60" s="43"/>
-      <c r="H60" s="232"/>
-      <c r="I60" s="233"/>
+      <c r="H60" s="140"/>
+      <c r="I60" s="141"/>
       <c r="J60" s="72"/>
       <c r="K60" s="75"/>
       <c r="L60" s="4"/>
@@ -4663,8 +4630,8 @@
       <c r="E61" s="43"/>
       <c r="F61" s="43"/>
       <c r="G61" s="43"/>
-      <c r="H61" s="232"/>
-      <c r="I61" s="233"/>
+      <c r="H61" s="140"/>
+      <c r="I61" s="141"/>
       <c r="J61" s="72"/>
       <c r="K61" s="75"/>
       <c r="L61" s="4"/>
@@ -4672,46 +4639,26 @@
     </row>
     <row r="62" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A62" s="53"/>
-      <c r="B62" s="76"/>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="232"/>
-      <c r="I62" s="233"/>
-      <c r="J62" s="72"/>
-      <c r="K62" s="75"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="54"/>
     </row>
     <row r="63" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A63" s="53"/>
-      <c r="B63" s="76"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="232"/>
-      <c r="I63" s="233"/>
-      <c r="J63" s="72"/>
-      <c r="K63" s="75"/>
       <c r="L63" s="4"/>
       <c r="M63" s="54"/>
     </row>
     <row r="64" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A64" s="53"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="54"/>
     </row>
@@ -4753,42 +4700,38 @@
     <row r="72" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A72" s="53"/>
       <c r="L72" s="4"/>
-      <c r="M72" s="54"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A73" s="53"/>
       <c r="L73" s="4"/>
-      <c r="M73" s="54"/>
-    </row>
-    <row r="74" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A74" s="53"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-    </row>
-    <row r="75" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A75" s="53"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-    </row>
-    <row r="76" spans="1:13" ht="15.6">
+      <c r="M73" s="4"/>
+    </row>
+    <row r="74" spans="1:13" ht="15.6">
+      <c r="A74" s="4"/>
+      <c r="L74" s="77"/>
+      <c r="M74" s="78"/>
+    </row>
+    <row r="75" spans="1:13" ht="15.6">
+      <c r="A75" s="4"/>
+      <c r="L75" s="77"/>
+      <c r="M75" s="78"/>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="4"/>
-      <c r="L76" s="77"/>
-      <c r="M76" s="78"/>
-    </row>
-    <row r="77" spans="1:13" ht="15.6">
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="4"/>
-      <c r="L77" s="77"/>
-      <c r="M77" s="78"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="4"/>
@@ -4862,59 +4805,23 @@
     <row r="103" spans="1:1">
       <c r="A103" s="4"/>
     </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="4"/>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H35:I35"/>
+  <mergeCells count="76">
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H48:I48"/>
     <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H24:I24"/>
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
@@ -4931,22 +4838,51 @@
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H49:I49"/>
     <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
